--- a/PatchTST_self_supervised/results/20250620实验数据结果.xlsx
+++ b/PatchTST_self_supervised/results/20250620实验数据结果.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="23837" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>目标域数据集</t>
   </si>
   <si>
     <t>s0.3548_m907</t>
-  </si>
-  <si>
-    <t>processed_data_55</t>
   </si>
   <si>
     <t>HTV2</t>
@@ -97,23 +94,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -773,7 +768,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -789,10 +784,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -804,9 +796,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,24 +805,18 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -841,9 +824,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1172,19 +1152,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="18.875" style="1" customWidth="1"/>
     <col min="2" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="1" customWidth="1"/>
     <col min="8" max="9" width="12.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="12.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1193,658 +1171,515 @@
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="19" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:13">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="B2" s="3">
         <v>41104</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="5">
+      <c r="D2" s="6"/>
+      <c r="E2" s="3">
         <v>41104</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="3">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="2">
         <v>41104</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="2">
-        <v>41104</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:13">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:10">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:10">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:13">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="7">
+        <v>0.521189</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.403594</v>
+      </c>
+      <c r="D4" s="8">
+        <f>(B4-C4)/B4</f>
+        <v>0.225628322930837</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.690004</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.614173</v>
+      </c>
+      <c r="G4" s="8">
+        <f>(E4-F4)/E4</f>
+        <v>0.109899362902244</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.567077</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.396591</v>
+      </c>
+      <c r="J4" s="16">
+        <f>(H4-I4)/H4</f>
+        <v>0.3006399483668</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:10">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="8">
-        <v>0.521189</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.403594</v>
-      </c>
-      <c r="D4" s="9">
-        <f t="shared" ref="D4:D9" si="0">(B4-C4)/C4</f>
-        <v>0.291369544641397</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.57807</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.381765</v>
-      </c>
-      <c r="G4" s="9">
-        <f t="shared" ref="G4:G9" si="1">(E4-F4)/F4</f>
-        <v>0.514203764095713</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0.690004</v>
-      </c>
-      <c r="I4" s="8">
-        <v>0.614173</v>
-      </c>
-      <c r="J4" s="9">
-        <f t="shared" ref="J4:J9" si="2">(H4-I4)/I4</f>
-        <v>0.123468468981867</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0.567077</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0.396591</v>
-      </c>
-      <c r="M4" s="20">
-        <f t="shared" ref="M4:M9" si="3">(K4-L4)/L4</f>
-        <v>0.429878640715498</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:13">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="7">
+        <v>0.40189</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.322133</v>
+      </c>
+      <c r="D5" s="8">
+        <f>(B5-C5)/B5</f>
+        <v>0.198454801064968</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.474914</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.406931</v>
+      </c>
+      <c r="G5" s="8">
+        <f>(E5-F5)/E5</f>
+        <v>0.143148022589353</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.449053</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.314293</v>
+      </c>
+      <c r="J5" s="16">
+        <f>(H5-I5)/H5</f>
+        <v>0.300098206670482</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:10">
+      <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8">
-        <v>0.40189</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.322133</v>
-      </c>
-      <c r="D5" s="9">
-        <f t="shared" si="0"/>
-        <v>0.24759028103299</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.461459</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0.290658</v>
-      </c>
-      <c r="G5" s="9">
-        <f t="shared" si="1"/>
-        <v>0.587635640512217</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0.474914</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0.406931</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" si="2"/>
-        <v>0.16706272070695</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0.449053</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0.314293</v>
-      </c>
-      <c r="M5" s="20">
-        <f t="shared" si="3"/>
-        <v>0.42877187847009</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:13">
-      <c r="A6" s="11" t="s">
+      <c r="B6" s="10">
+        <v>0.5503643</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.407083</v>
+      </c>
+      <c r="D6" s="11">
+        <f>(B6-C6)/B6</f>
+        <v>0.260339015448495</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.6562253</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.606579</v>
+      </c>
+      <c r="G6" s="11">
+        <f>(E6-F6)/E6</f>
+        <v>0.0756543522476199</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.62741633</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0.3917456</v>
+      </c>
+      <c r="J6" s="17">
+        <f>(H6-I6)/H6</f>
+        <v>0.375620969253382</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:10">
+      <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12">
-        <v>0.5503643</v>
-      </c>
-      <c r="C6" s="12">
-        <v>0.407083</v>
-      </c>
-      <c r="D6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.35197072832813</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0.6479466</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0.365977</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="1"/>
-        <v>0.770457159876167</v>
-      </c>
-      <c r="H6" s="12">
-        <v>0.6562253</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0.606579</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="2"/>
-        <v>0.0818463876922875</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0.62741633</v>
-      </c>
-      <c r="L6" s="12">
-        <v>0.3917456</v>
-      </c>
-      <c r="M6" s="15">
-        <f t="shared" si="3"/>
-        <v>0.601591262288587</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:13">
-      <c r="A7" s="11" t="s">
+      <c r="B7" s="10">
+        <v>0.4193403</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.331213</v>
+      </c>
+      <c r="D7" s="11">
+        <f>(B7-C7)/B7</f>
+        <v>0.210157001366194</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.471443</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.446568</v>
+      </c>
+      <c r="G7" s="11">
+        <f>(E7-F7)/E7</f>
+        <v>0.0527635366311515</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.469504</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0.3217296</v>
+      </c>
+      <c r="J7" s="17">
+        <f>(H7-I7)/H7</f>
+        <v>0.314745774263904</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:10">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="12">
-        <v>0.4193403</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0.331213</v>
-      </c>
-      <c r="D7" s="13">
-        <f t="shared" si="0"/>
-        <v>0.266074399253653</v>
-      </c>
-      <c r="E7" s="12">
-        <v>0.4681383</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0.2933883</v>
-      </c>
-      <c r="G7" s="15">
-        <f t="shared" si="1"/>
-        <v>0.595627023981529</v>
-      </c>
-      <c r="H7" s="12">
-        <v>0.471443</v>
-      </c>
-      <c r="I7" s="12">
-        <v>0.446568</v>
-      </c>
-      <c r="J7" s="13">
-        <f t="shared" si="2"/>
-        <v>0.0557026029630425</v>
-      </c>
-      <c r="K7" s="12">
-        <v>0.469504</v>
-      </c>
-      <c r="L7" s="12">
-        <v>0.3217296</v>
-      </c>
-      <c r="M7" s="21">
-        <f t="shared" si="3"/>
-        <v>0.459312416389415</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:13">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="7">
+        <v>0.113223</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.090094</v>
+      </c>
+      <c r="D8" s="8">
+        <f>(B8-C8)/B8</f>
+        <v>0.204278282681081</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.113423</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.111815</v>
+      </c>
+      <c r="G8" s="8">
+        <f>(E8-F8)/E8</f>
+        <v>0.0141770187704434</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.141684</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.113457</v>
+      </c>
+      <c r="J8" s="16">
+        <f>(H8-I8)/H8</f>
+        <v>0.199225035995596</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:10">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8">
-        <v>0.113223</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0.090094</v>
-      </c>
-      <c r="D8" s="9">
-        <f t="shared" si="0"/>
-        <v>0.256720758319089</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.127494</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.082492</v>
-      </c>
-      <c r="G8" s="9">
-        <f t="shared" si="1"/>
-        <v>0.545531687921253</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0.113423</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0.111815</v>
-      </c>
-      <c r="J8" s="9">
-        <f t="shared" si="2"/>
-        <v>0.0143808970173948</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0.141684</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0.113457</v>
-      </c>
-      <c r="M8" s="20">
-        <f t="shared" si="3"/>
-        <v>0.248790290594675</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>0.141978</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>0.10567</v>
       </c>
-      <c r="D9" s="9">
-        <f t="shared" si="0"/>
-        <v>0.34359799375414</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.1708017</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.0701823</v>
-      </c>
-      <c r="G9" s="9">
-        <f t="shared" si="1"/>
-        <v>1.43368627132482</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="D9" s="8">
+        <f>(B9-C9)/B9</f>
+        <v>0.255729760948879</v>
+      </c>
+      <c r="E9" s="7">
         <v>0.1275373</v>
       </c>
-      <c r="I9" s="8">
+      <c r="F9" s="7">
         <v>0.136505</v>
       </c>
-      <c r="J9" s="9">
-        <f t="shared" si="2"/>
-        <v>-0.0656950294860994</v>
-      </c>
-      <c r="K9" s="8">
+      <c r="G9" s="8">
+        <f>(E9-F9)/E9</f>
+        <v>-0.0703143315720185</v>
+      </c>
+      <c r="H9" s="7">
         <v>0.1154297</v>
       </c>
-      <c r="L9" s="22">
+      <c r="I9" s="18">
         <v>0.1090773</v>
       </c>
-      <c r="M9" s="20">
-        <f t="shared" si="3"/>
-        <v>0.0582375984737429</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:12">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:12">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:12">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:12">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="23"/>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:12">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="18"/>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:12">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="23"/>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:12">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="23"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:12">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="23"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:12">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="23"/>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="1:12">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" spans="1:12">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="1:12">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="1:12">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-    </row>
-    <row r="25" ht="30" customHeight="1" spans="1:12">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" spans="1:12">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="23"/>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:12">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="23"/>
-    </row>
-    <row r="28" ht="30" customHeight="1" spans="1:12">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="23"/>
-    </row>
-    <row r="29" ht="30" customHeight="1" spans="1:12">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="23"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" spans="1:12">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" ht="30" customHeight="1" spans="1:12">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="23"/>
+      <c r="J9" s="16">
+        <f>(H9-I9)/H9</f>
+        <v>0.0550326302502735</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:9">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:9">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:9">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:9">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:9">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:9">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:9">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:9">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:9">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:9">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:9">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:9">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:9">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:9">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:9">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:9">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:9">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:9">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:9">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:9">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="14">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="B23:I23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="K24:L24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
